--- a/sheets/대금율보/검수/물레방아 도는데.xlsx
+++ b/sheets/대금율보/검수/물레방아 도는데.xlsx
@@ -4244,7 +4244,6 @@
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-‹
 汰浹</t>
         </is>
       </c>
@@ -4311,8 +4310,7 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -4333,7 +4331,6 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-‹
 –汰</t>
         </is>
       </c>
@@ -4390,16 +4387,14 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="K6" s="24"/>
@@ -4527,8 +4522,7 @@
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕
-‹</t>
+          <t xml:space="preserve">潕</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -4587,7 +4581,6 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕汰
-‹
 –潕</t>
         </is>
       </c>
@@ -4711,8 +4704,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -4723,7 +4715,6 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-‹
 –潕</t>
         </is>
       </c>
@@ -4885,8 +4876,7 @@
       <c r="C17" s="23"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -4993,7 +4983,6 @@
       <c r="H19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰∧
-‹
 淋</t>
         </is>
       </c>
@@ -5005,8 +4994,7 @@
       <c r="J19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-汰浹
-‹</t>
+汰浹</t>
         </is>
       </c>
       <c r="K19" s="22"/>

--- a/sheets/대금율보/검수/물레방아 도는데.xlsx
+++ b/sheets/대금율보/검수/물레방아 도는데.xlsx
@@ -4176,22 +4176,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="83.33" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="74.53" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="74.53" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="74.53" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="74.53" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="74.53" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="25" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="74.53" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="74.53" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="74.53" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="74.53" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="74.53" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="74.53" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="74.53" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="74.53" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="74.53" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="74.53" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="74.53" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="25" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="K18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="74.53" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="K19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="74.53" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="23"/>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="K20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="74.53" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="74.53" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -5114,6 +5114,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="48"/>
 </worksheet>
 </file>